--- a/data_extactor/batch_10_fa/trimmed/batch_0058_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0058_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | انعطاف‌پذیری بدن | قدرت بدنی بالاتنه | ثبات دست و بازو</t>
+          <t>مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایستادن طولانی‌مدت حین کار | استفاده مستمر از دست‌ها برای کار با ابزارها | توجه به ایمنی و بهداشت سایر کارکنان | محیط سرپوشیده با تهویهٔ مطبوع | کار گروهی و تیمی | گفت‌وگوی حضوری با همکاران | ارتباط مداوم با دیگران</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | کارکنان کانتر و فست‌فود | کارگران آماده‌سازی غذا | کارگران ساده بخش تولید | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | خدمتکاران و نظافتچیان منازل و هتل‌ها</t>
+          <t>کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | کمک‌کارگران خطوط تولید | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | خدمتکاران و نظافتچیان منازل و هتل‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | دید نزدیک | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>باریستاها | متصدیان بار | صندوقداران | نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | کارکنان کانتر و فست‌فود | مدیران خدمات پذیرایی و غذا | سالن‌کاران و گارسون‌ها</t>
+          <t>باریستاها | متصدیان بار و نوشیدنی | صندوق‌داران | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | مدیران خدمات پذیرایی و غذا و نوشیدنی | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | زبان انگلیسی | تولید و فراوری | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | قدرت بدنی بالاتنه | دید نزدیک | حساسیت به مسئله | درک شفاهی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | قدرت تنه | بینایی نزدیک | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران آماده‌سازی غذا | کارکنان کانتر و فست‌فود | نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | ظرف‌شویان | سالن‌کاران و گارسون‌ها | آشپزهای رستوران | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا</t>
+          <t>کارگران آماده‌سازی غذا | کارگران پیشخوان و فست‌فود | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | پیش‌خدمتان و گارسون‌ها | آشپزان رستوران | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | آموزش و پرورش | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران تاسیسات و نگهداری ساختمان | سرپرستان رده اول کمک‌کارگران، کارگران ساده و متصدیان حمل بار دستی | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده اول کارکنان خدمات فردی | سرپرستان رده اول نیروهای حراست و نگهبانی | خدمتکاران و نظافتچیان منازل و هتل‌ها | هماهنگ‌کنندگان امور بازیافت مواد</t>
+          <t>مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول کارکنان حراست و انتظامات | خدمتکاران و نظافتچیان منازل و هتل‌ها | هماهنگ‌کنندگان امور بازیافت</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ریاضیات | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | مکانیک</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مکانیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | وضوح گفتار | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>سرپرستان رده اول مشاغل ساختمانی و استخراج | سرپرستان رده اول کارگران کشاورزی، شیلات و جنگلداری | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول مکانیک‌ها، نصابان و تعمیرکاران | تکنسین‌های جنگلداری و حفاظت از منابع طبیعی | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی نگهداری و تعمیرات</t>
+          <t>سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی تعمیرات و نگهداری تاسیسات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>تی شیشه‌شور و جمع‌کننده آب | Eko | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+          <t>تی شیشه‌شور و جمع‌کننده آب | Eko | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | تی شیشه‌شوی</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>قدرت بدنی بالاتنه | دید نزدیک | انعطاف‌پذیری بدن | قدرت ایستا | چابکی دستی | ثبات دست و بازو | حساسیت به مسئله</t>
+          <t>قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | مهارت دستی | ثبات دست و بازو | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نظافتچیان وسایل نقلیه و تجهیزات | کارگران ساختمانی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | ساب‌زنان و پرداخت‌کاران کف | کارگران باغبانی، فضای سبز و نگهداری محوطه | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارگران عمومی نگهداری و تعمیرات</t>
+          <t>شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران ساختمانی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | ساب‌زنان و پرداخت‌کاران کف | کارگران باغبانی، فضای سبز و نگهداری محوطه | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارگران عمومی تعمیرات و نگهداری تاسیسات</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت بدنی بالاتنه | دید نزدیک | انعطاف‌پذیری بدن | استقامت بدنی | بیان شفاهی | درک شفاهی</t>
+          <t>قدرت تنه | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نیروهای خدماتی سالن پذیرایی، سلف‌سرویس و دستیاران متصدی بار | ظرف‌شویان | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران خشکشویی و رختشویخانه | متصدیان رختکن و اتاق تعویض لباس</t>
+          <t>کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران خشکشویی و رختشویخانه | متصدیان رختکن، امانات و اتاق پرو</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | شیمی | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | قدرت ایستا | قدرت بدنی بالاتنه | دید نزدیک | حساسیت به مسئله | درک شفاهی</t>
+          <t>مهارت دستی | ثبات دست و بازو | قدرت ایستا | قدرت تنه | بینایی نزدیک | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | خدمتکاران و نظافتچیان منازل و هتل‌ها | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | کارگران سم‌پاشی و کنترل آفات | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی نگهداری و تعمیرات | نظافتچیان وسایل نقلیه و تجهیزات</t>
+          <t>سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | خدمتکاران و نظافتچیان منازل و هتل‌ها | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | کارگران سم‌پاشی و دفع آفات | کارگران باغبانی، فضای سبز و نگهداری محوطه | کارگران عمومی تعمیرات و نگهداری تاسیسات | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | دید دور</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی دور</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | کارگران مزارع، زراعت، نهالستان و گلخانه | کارگران امحا و پاکسازی مواد خطرناک | کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌ها در فضای سبز | تکنسین‌های تخلیه چاه و لایروبی شبکه فاضلاب</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌های علوم و بهداشت محیط زیست | کارگران زراعت، نهالستان و گلخانه | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران باغبانی، فضای سبز و نگهداری محوطه | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IBM Notes | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Facebook</t>
+          <t>Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>هماهنگی چندعضو | چابکی دستی | قدرت بدنی بالاتنه | ثبات دست و بازو | انعطاف‌پذیری بدن | قدرت ایستا | دید نزدیک</t>
+          <t>هماهنگی چند عضو | مهارت دستی | قدرت تنه | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات کشاورزی | کارگران ساختمانی | کارگران مزارع، زراعت، نهالستان و گلخانه | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران عمومی نگهداری و تعمیرات | هرس‌کاران و شاخه‌زن‌های درختان</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | کارگران ساختمانی | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران عمومی تعمیرات و نگهداری تاسیسات | هرس‌کنندگان و پیرایندگان درختان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
